--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260618.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260618.xlsx
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.77%</t>
+          <t>9.68%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>4,486,000</t>
+          <t>23,892,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.99%</t>
+          <t>8.67%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>23,292,000</t>
+          <t>4,486,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.85%</t>
+          <t>8.44%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.42%</t>
+          <t>7.17%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.41%</t>
+          <t>5.18%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>4.91%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.85%</t>
+          <t>4.75%</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.29%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>12,466,000</t>
+          <t>5,191,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.18%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>5,191,000</t>
+          <t>12,466,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>4.05%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>3.78%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.71%</t>
+          <t>3.78%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.70%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.41%</t>
         </is>
       </c>
     </row>
@@ -924,51 +924,51 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2,267,000</t>
+          <t>5,058,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>4,927,000</t>
+          <t>2,267,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1085,22 +1085,22 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>7,307,000</t>
+          <t>6,484,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1122,183 +1122,183 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,034,000</t>
+          <t>7,307,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,334,000</t>
+          <t>1,034,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>6,275,000</t>
+          <t>1,334,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>258,000</t>
+          <t>6,275,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>3,528,000</t>
+          <t>258,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,642,000</t>
+          <t>11,635,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,635,000</t>
+          <t>3,528,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,645,000</t>
+          <t>1,642,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1386,46 +1386,46 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>3,988,000</t>
+          <t>1,966,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>3,988,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,83 +1437,83 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,741,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,466,000</t>
+          <t>1,508,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>329,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,39 +1525,39 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>329,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>5,822,164,391</t>
+          <t>4,491,865,572</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-983,075,567</t>
+          <t>-3,023,511,393</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
